--- a/artfynd/A 52678-2020 artfynd.xlsx
+++ b/artfynd/A 52678-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52678-2020 artfynd.xlsx
+++ b/artfynd/A 52678-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY280"/>
+  <dimension ref="A1:AY279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25996,10 +25996,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>88404326</v>
+        <v>88362141</v>
       </c>
       <c r="B228" t="n">
-        <v>56395</v>
+        <v>89356</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -26008,43 +26008,38 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Sventkullen, Njakafjäll, Ås lm</t>
+          <t>Saxnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>530581.2767862017</v>
+        <v>530881.0170587201</v>
       </c>
       <c r="R228" t="n">
-        <v>7208633.227675344</v>
+        <v>7209061.110789069</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -26101,22 +26096,22 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Billy Lindblom, Linda Sandberg</t>
+          <t>Billy Lindblom, Tobias Pettersson, Roger Olofsson, Linda Sandgren</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>88362141</v>
+        <v>88362064</v>
       </c>
       <c r="B229" t="n">
-        <v>89356</v>
+        <v>89317</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -26125,25 +26120,25 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>5447</v>
+        <v>3242</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -26153,10 +26148,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>530881.0170587201</v>
+        <v>530381.011311123</v>
       </c>
       <c r="R229" t="n">
-        <v>7209061.110789069</v>
+        <v>7208455.575880114</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -26225,10 +26220,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>88362064</v>
+        <v>88362097</v>
       </c>
       <c r="B230" t="n">
-        <v>89317</v>
+        <v>89673</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -26241,21 +26236,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>3242</v>
+        <v>658</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -26265,10 +26260,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>530381.011311123</v>
+        <v>530356.0017501765</v>
       </c>
       <c r="R230" t="n">
-        <v>7208455.575880114</v>
+        <v>7208623.308803847</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -26337,10 +26332,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>88362097</v>
+        <v>88362083</v>
       </c>
       <c r="B231" t="n">
-        <v>89673</v>
+        <v>89832</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -26349,25 +26344,25 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -26377,10 +26372,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>530356.0017501765</v>
+        <v>530291.8019954266</v>
       </c>
       <c r="R231" t="n">
-        <v>7208623.308803847</v>
+        <v>7208562.570565483</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -26449,10 +26444,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>88362083</v>
+        <v>88404479</v>
       </c>
       <c r="B232" t="n">
-        <v>89832</v>
+        <v>89410</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -26461,38 +26456,38 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Saxnäs, Ås lm</t>
+          <t>Sventkullen, Njakafjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>530291.8019954266</v>
+        <v>531271.3423317604</v>
       </c>
       <c r="R232" t="n">
-        <v>7208562.570565483</v>
+        <v>7209081.680285643</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -26549,22 +26544,22 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Billy Lindblom, Tobias Pettersson, Roger Olofsson, Linda Sandgren</t>
+          <t>Yasmine Kindlund, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>88404479</v>
+        <v>88404422</v>
       </c>
       <c r="B233" t="n">
-        <v>89410</v>
+        <v>89777</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -26577,21 +26572,16 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -26601,10 +26591,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>531271.3423317604</v>
+        <v>530222.7114949637</v>
       </c>
       <c r="R233" t="n">
-        <v>7209081.680285643</v>
+        <v>7208566.100702723</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26666,17 +26656,17 @@
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isak Vahlström</t>
+          <t>Billy Lindblom, Linda Sandberg</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>88404422</v>
+        <v>88404397</v>
       </c>
       <c r="B234" t="n">
-        <v>89777</v>
+        <v>89673</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -26689,16 +26679,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6040186</v>
+        <v>658</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -26708,10 +26703,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>530222.7114949637</v>
+        <v>530238.9286289784</v>
       </c>
       <c r="R234" t="n">
-        <v>7208566.100702723</v>
+        <v>7208554.41725482</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -26780,10 +26775,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>88404397</v>
+        <v>88404261</v>
       </c>
       <c r="B235" t="n">
-        <v>89673</v>
+        <v>78072</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -26796,21 +26791,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>658</v>
+        <v>229821</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -26820,10 +26815,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>530238.9286289784</v>
+        <v>531755.865506908</v>
       </c>
       <c r="R235" t="n">
-        <v>7208554.41725482</v>
+        <v>7209324.982205604</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -26885,17 +26880,17 @@
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Billy Lindblom, Linda Sandberg</t>
+          <t>Yasmine Kindlund, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>88404261</v>
+        <v>88404529</v>
       </c>
       <c r="B236" t="n">
-        <v>78072</v>
+        <v>81236</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -26908,21 +26903,21 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>229821</v>
+        <v>1312</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -26932,10 +26927,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>531755.865506908</v>
+        <v>530304.2670852194</v>
       </c>
       <c r="R236" t="n">
-        <v>7209324.982205604</v>
+        <v>7208628.283127435</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -26997,17 +26992,17 @@
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isak Vahlström</t>
+          <t>Billy Lindblom, Linda Sandberg</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>88404529</v>
+        <v>88404523</v>
       </c>
       <c r="B237" t="n">
-        <v>81236</v>
+        <v>89410</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -27020,21 +27015,21 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -27044,10 +27039,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>530304.2670852194</v>
+        <v>530542.1492747435</v>
       </c>
       <c r="R237" t="n">
-        <v>7208628.283127435</v>
+        <v>7208524.080106997</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27116,10 +27111,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>88404523</v>
+        <v>88404569</v>
       </c>
       <c r="B238" t="n">
-        <v>89410</v>
+        <v>76909</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -27132,21 +27127,21 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>5432</v>
+        <v>6437</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -27156,10 +27151,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>530542.1492747435</v>
+        <v>531752.5000645099</v>
       </c>
       <c r="R238" t="n">
-        <v>7208524.080106997</v>
+        <v>7209322.831164665</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -27221,17 +27216,17 @@
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Billy Lindblom, Linda Sandberg</t>
+          <t>Yasmine Kindlund, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>88404569</v>
+        <v>88362043</v>
       </c>
       <c r="B239" t="n">
-        <v>76909</v>
+        <v>89388</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -27244,34 +27239,34 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>6437</v>
+        <v>1108</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Sventkullen, Njakafjäll, Ås lm</t>
+          <t>Saxnäs, Ås lm</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>531752.5000645099</v>
+        <v>530571.1490172638</v>
       </c>
       <c r="R239" t="n">
-        <v>7209322.831164665</v>
+        <v>7208753.290355315</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -27328,22 +27323,22 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Isak Vahlström</t>
+          <t>Billy Lindblom, Tobias Pettersson, Roger Olofsson, Linda Sandgren</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>88362043</v>
+        <v>88362107</v>
       </c>
       <c r="B240" t="n">
-        <v>89388</v>
+        <v>89406</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -27356,21 +27351,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -27380,10 +27375,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>530571.1490172638</v>
+        <v>530552.7745067251</v>
       </c>
       <c r="R240" t="n">
-        <v>7208753.290355315</v>
+        <v>7208644.783035323</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27452,10 +27447,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>88362107</v>
+        <v>88362069</v>
       </c>
       <c r="B241" t="n">
-        <v>89406</v>
+        <v>78596</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -27464,25 +27459,25 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -27492,10 +27487,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>530552.7745067251</v>
+        <v>530290.0963293395</v>
       </c>
       <c r="R241" t="n">
-        <v>7208644.783035323</v>
+        <v>7208438.570851604</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27564,10 +27559,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>88362069</v>
+        <v>88362052</v>
       </c>
       <c r="B242" t="n">
-        <v>78596</v>
+        <v>89388</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -27576,25 +27571,25 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -27604,10 +27599,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>530290.0963293395</v>
+        <v>530577.5225490197</v>
       </c>
       <c r="R242" t="n">
-        <v>7208438.570851604</v>
+        <v>7208586.221341585</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27676,10 +27671,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>88362052</v>
+        <v>89168994</v>
       </c>
       <c r="B243" t="n">
-        <v>89388</v>
+        <v>89392</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -27692,34 +27687,34 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Saxnäs, Ås lm</t>
+          <t>Rödingsjöbäcken, Njakafjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>530577.5225490197</v>
+        <v>529780.6730671271</v>
       </c>
       <c r="R243" t="n">
-        <v>7208586.221341585</v>
+        <v>7207735.149640793</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27746,7 +27741,7 @@
       </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>2020-09-19</t>
+          <t>2020-11-19</t>
         </is>
       </c>
       <c r="Z243" t="inlineStr">
@@ -27756,7 +27751,7 @@
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2020-09-19</t>
+          <t>2020-11-19</t>
         </is>
       </c>
       <c r="AB243" t="inlineStr">
@@ -27776,22 +27771,22 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Billy Lindblom, Tobias Pettersson, Roger Olofsson, Linda Sandgren</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>89168994</v>
+        <v>89169049</v>
       </c>
       <c r="B244" t="n">
-        <v>89392</v>
+        <v>78503</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -27800,25 +27795,25 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -27828,10 +27823,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>529780.6730671271</v>
+        <v>529692.8878622223</v>
       </c>
       <c r="R244" t="n">
-        <v>7207735.149640793</v>
+        <v>7207997.103850742</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -27900,10 +27895,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>89169049</v>
+        <v>89168965</v>
       </c>
       <c r="B245" t="n">
-        <v>78503</v>
+        <v>89356</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -27916,21 +27911,21 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -27940,10 +27935,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>529692.8878622223</v>
+        <v>529923.8699507392</v>
       </c>
       <c r="R245" t="n">
-        <v>7207997.103850742</v>
+        <v>7207738.699391033</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -28012,7 +28007,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>89168965</v>
+        <v>89168966</v>
       </c>
       <c r="B246" t="n">
         <v>89356</v>
@@ -28052,10 +28047,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>529923.8699507392</v>
+        <v>529803.0205869442</v>
       </c>
       <c r="R246" t="n">
-        <v>7207738.699391033</v>
+        <v>7208000.741906621</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -28124,10 +28119,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>89168966</v>
+        <v>89169124</v>
       </c>
       <c r="B247" t="n">
-        <v>89356</v>
+        <v>89410</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -28136,25 +28131,25 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -28164,10 +28159,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>529803.0205869442</v>
+        <v>529752.3219966873</v>
       </c>
       <c r="R247" t="n">
-        <v>7208000.741906621</v>
+        <v>7207985.846181728</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -28236,10 +28231,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>89169124</v>
+        <v>89169114</v>
       </c>
       <c r="B248" t="n">
-        <v>89410</v>
+        <v>89406</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -28252,21 +28247,21 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -28276,10 +28271,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>529752.3219966873</v>
+        <v>529761.6266808036</v>
       </c>
       <c r="R248" t="n">
-        <v>7207985.846181728</v>
+        <v>7207732.843220077</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -28348,10 +28343,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>89169114</v>
+        <v>89169046</v>
       </c>
       <c r="B249" t="n">
-        <v>89406</v>
+        <v>78570</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -28364,21 +28359,21 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -28388,10 +28383,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>529761.6266808036</v>
+        <v>529626.1508865874</v>
       </c>
       <c r="R249" t="n">
-        <v>7207732.843220077</v>
+        <v>7208188.997705467</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -28460,10 +28455,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>89169046</v>
+        <v>89169057</v>
       </c>
       <c r="B250" t="n">
-        <v>78570</v>
+        <v>73698</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -28476,21 +28471,21 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -28500,10 +28495,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>529626.1508865874</v>
+        <v>529895.8454599926</v>
       </c>
       <c r="R250" t="n">
-        <v>7208188.997705467</v>
+        <v>7207702.018183826</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -28572,10 +28567,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>89169057</v>
+        <v>89169149</v>
       </c>
       <c r="B251" t="n">
-        <v>73698</v>
+        <v>85703</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -28588,21 +28583,21 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>1467</v>
+        <v>510</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -28612,10 +28607,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>529895.8454599926</v>
+        <v>529900.0190803548</v>
       </c>
       <c r="R251" t="n">
-        <v>7207702.018183826</v>
+        <v>7207708.408918458</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -28684,10 +28679,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>89169149</v>
+        <v>89169116</v>
       </c>
       <c r="B252" t="n">
-        <v>85703</v>
+        <v>89406</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -28700,21 +28695,21 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>510</v>
+        <v>1204</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -28724,10 +28719,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>529900.0190803548</v>
+        <v>529802.596902355</v>
       </c>
       <c r="R252" t="n">
-        <v>7207708.408918458</v>
+        <v>7208000.737671886</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -28796,10 +28791,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>89169116</v>
+        <v>89169010</v>
       </c>
       <c r="B253" t="n">
-        <v>89406</v>
+        <v>56395</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -28812,34 +28807,39 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P253" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Njakafjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>529802.596902355</v>
+        <v>529992.5326126096</v>
       </c>
       <c r="R253" t="n">
-        <v>7208000.737671886</v>
+        <v>7207863.823522408</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28908,10 +28908,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>89169010</v>
+        <v>89169134</v>
       </c>
       <c r="B254" t="n">
-        <v>56395</v>
+        <v>77506</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -28924,39 +28924,34 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P254" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Njakafjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>529992.5326126096</v>
+        <v>529706.026315123</v>
       </c>
       <c r="R254" t="n">
-        <v>7207863.823522408</v>
+        <v>7207996.811496741</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -29025,10 +29020,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>89169134</v>
+        <v>89169126</v>
       </c>
       <c r="B255" t="n">
-        <v>77506</v>
+        <v>89410</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -29041,21 +29036,21 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -29065,10 +29060,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>529706.026315123</v>
+        <v>529628.191347776</v>
       </c>
       <c r="R255" t="n">
-        <v>7207996.811496741</v>
+        <v>7208111.573194392</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -29137,10 +29132,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>89169126</v>
+        <v>89169073</v>
       </c>
       <c r="B256" t="n">
-        <v>89410</v>
+        <v>89673</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -29153,21 +29148,21 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -29177,10 +29172,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>529628.191347776</v>
+        <v>529848.2954523729</v>
       </c>
       <c r="R256" t="n">
-        <v>7208111.573194392</v>
+        <v>7207964.797862719</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -29249,10 +29244,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>89169073</v>
+        <v>89169013</v>
       </c>
       <c r="B257" t="n">
-        <v>89673</v>
+        <v>56395</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -29265,34 +29260,39 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P257" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Njakafjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>529848.2954523729</v>
+        <v>529760.3203517286</v>
       </c>
       <c r="R257" t="n">
-        <v>7207964.797862719</v>
+        <v>7207693.890463361</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -29361,10 +29361,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>89169013</v>
+        <v>89169150</v>
       </c>
       <c r="B258" t="n">
-        <v>56395</v>
+        <v>85703</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -29377,39 +29377,34 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
-      <c r="M258" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P258" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Njakafjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>529760.3203517286</v>
+        <v>529746.9913810845</v>
       </c>
       <c r="R258" t="n">
-        <v>7207693.890463361</v>
+        <v>7207968.017737567</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29478,10 +29473,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>89169150</v>
+        <v>89169142</v>
       </c>
       <c r="B259" t="n">
-        <v>85703</v>
+        <v>81236</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -29494,21 +29489,21 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -29518,10 +29513,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>529746.9913810845</v>
+        <v>529766.3205550178</v>
       </c>
       <c r="R259" t="n">
-        <v>7207968.017737567</v>
+        <v>7207984.293015094</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -29590,10 +29585,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>89169142</v>
+        <v>89169118</v>
       </c>
       <c r="B260" t="n">
-        <v>81236</v>
+        <v>89406</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -29606,21 +29601,21 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -29630,10 +29625,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>529766.3205550178</v>
+        <v>529748.6565843245</v>
       </c>
       <c r="R260" t="n">
-        <v>7207984.293015094</v>
+        <v>7207970.996901054</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -29702,10 +29697,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>89169118</v>
+        <v>89169045</v>
       </c>
       <c r="B261" t="n">
-        <v>89406</v>
+        <v>78570</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -29718,21 +29713,21 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -29742,10 +29737,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>529748.6565843245</v>
+        <v>529663.4568928075</v>
       </c>
       <c r="R261" t="n">
-        <v>7207970.996901054</v>
+        <v>7208101.766989779</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -29814,10 +29809,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>89169045</v>
+        <v>89169125</v>
       </c>
       <c r="B262" t="n">
-        <v>78570</v>
+        <v>89410</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -29830,21 +29825,21 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -29854,10 +29849,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>529663.4568928075</v>
+        <v>529706.4584321716</v>
       </c>
       <c r="R262" t="n">
-        <v>7208101.766989779</v>
+        <v>7207995.969366582</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -29926,10 +29921,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>89169125</v>
+        <v>89169115</v>
       </c>
       <c r="B263" t="n">
-        <v>89410</v>
+        <v>89406</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -29942,21 +29937,21 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -29966,10 +29961,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>529706.4584321716</v>
+        <v>529849.1428317921</v>
       </c>
       <c r="R263" t="n">
-        <v>7207995.969366582</v>
+        <v>7207964.806345213</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -30038,10 +30033,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>89169115</v>
+        <v>89169048</v>
       </c>
       <c r="B264" t="n">
-        <v>89406</v>
+        <v>78570</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -30054,21 +30049,21 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -30078,10 +30073,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>529849.1428317921</v>
+        <v>529690.9805194518</v>
       </c>
       <c r="R264" t="n">
-        <v>7207964.806345213</v>
+        <v>7208060.990008474</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -30150,10 +30145,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>89169048</v>
+        <v>89169058</v>
       </c>
       <c r="B265" t="n">
-        <v>78570</v>
+        <v>73698</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -30166,21 +30161,21 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -30190,10 +30185,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>529690.9805194518</v>
+        <v>530005.3416771581</v>
       </c>
       <c r="R265" t="n">
-        <v>7208060.990008474</v>
+        <v>7207854.217911328</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -30262,10 +30257,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>89169058</v>
+        <v>89168996</v>
       </c>
       <c r="B266" t="n">
-        <v>73698</v>
+        <v>89392</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -30278,21 +30273,21 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>1467</v>
+        <v>1202</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -30302,10 +30297,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>530005.3416771581</v>
+        <v>529581.4943099021</v>
       </c>
       <c r="R266" t="n">
-        <v>7207854.217911328</v>
+        <v>7208248.646683523</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -30374,10 +30369,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>89168996</v>
+        <v>89169089</v>
       </c>
       <c r="B267" t="n">
-        <v>89392</v>
+        <v>89777</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -30390,21 +30385,16 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -30414,10 +30404,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>529581.4943099021</v>
+        <v>530016.3196801463</v>
       </c>
       <c r="R267" t="n">
-        <v>7208248.646683523</v>
+        <v>7207858.137541567</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -30486,10 +30476,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>89169089</v>
+        <v>89169156</v>
       </c>
       <c r="B268" t="n">
-        <v>89777</v>
+        <v>78602</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -30498,20 +30488,25 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>6040186</v>
+        <v>6463</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -30521,10 +30516,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>530016.3196801463</v>
+        <v>529698.6235467466</v>
       </c>
       <c r="R268" t="n">
-        <v>7207858.137541567</v>
+        <v>7208059.373291588</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -30593,10 +30588,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>89169156</v>
+        <v>89168995</v>
       </c>
       <c r="B269" t="n">
-        <v>78602</v>
+        <v>89392</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -30605,25 +30600,25 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -30633,10 +30628,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>529698.6235467466</v>
+        <v>529750.7623615701</v>
       </c>
       <c r="R269" t="n">
-        <v>7208059.373291588</v>
+        <v>7207972.287574266</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -30705,10 +30700,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>89168995</v>
+        <v>89169148</v>
       </c>
       <c r="B270" t="n">
-        <v>89392</v>
+        <v>85703</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -30721,21 +30716,21 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
@@ -30745,10 +30740,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>529750.7623615701</v>
+        <v>529765.1685332356</v>
       </c>
       <c r="R270" t="n">
-        <v>7207972.287574266</v>
+        <v>7207717.641348752</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -30817,10 +30812,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>89169148</v>
+        <v>89169033</v>
       </c>
       <c r="B271" t="n">
-        <v>85703</v>
+        <v>78596</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -30829,25 +30824,25 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>510</v>
+        <v>6462</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
@@ -30857,10 +30852,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>529765.1685332356</v>
+        <v>529590.1604737368</v>
       </c>
       <c r="R271" t="n">
-        <v>7207717.641348752</v>
+        <v>7208229.266267547</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -30929,10 +30924,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>89169033</v>
+        <v>89169043</v>
       </c>
       <c r="B272" t="n">
-        <v>78596</v>
+        <v>78570</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -30941,25 +30936,25 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
@@ -30969,10 +30964,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>529590.1604737368</v>
+        <v>529731.1882952368</v>
       </c>
       <c r="R272" t="n">
-        <v>7208229.266267547</v>
+        <v>7207980.556749435</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -31041,10 +31036,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>89169043</v>
+        <v>89169087</v>
       </c>
       <c r="B273" t="n">
-        <v>78570</v>
+        <v>78603</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -31053,25 +31048,25 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
@@ -31081,10 +31076,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>529731.1882952368</v>
+        <v>529663.4653126007</v>
       </c>
       <c r="R273" t="n">
-        <v>7207980.556749435</v>
+        <v>7208100.920668352</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -31153,10 +31148,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>89169087</v>
+        <v>89169044</v>
       </c>
       <c r="B274" t="n">
-        <v>78603</v>
+        <v>78570</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -31165,25 +31160,25 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -31193,10 +31188,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>529663.4653126007</v>
+        <v>529699.051437906</v>
       </c>
       <c r="R274" t="n">
-        <v>7208100.920668352</v>
+        <v>7208058.954344873</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -31265,10 +31260,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>89169044</v>
+        <v>89169059</v>
       </c>
       <c r="B275" t="n">
-        <v>78570</v>
+        <v>73698</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -31281,21 +31276,21 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -31305,10 +31300,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>529699.051437906</v>
+        <v>529828.8907460273</v>
       </c>
       <c r="R275" t="n">
-        <v>7208058.954344873</v>
+        <v>7207998.461288404</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -31377,10 +31372,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>89169059</v>
+        <v>89169133</v>
       </c>
       <c r="B276" t="n">
-        <v>73698</v>
+        <v>77506</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -31393,21 +31388,21 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -31417,10 +31412,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>529828.8907460273</v>
+        <v>530006.1848296403</v>
       </c>
       <c r="R276" t="n">
-        <v>7207998.461288404</v>
+        <v>7207854.649634163</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -31489,10 +31484,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>89169133</v>
+        <v>89169170</v>
       </c>
       <c r="B277" t="n">
-        <v>77506</v>
+        <v>89780</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -31501,25 +31496,25 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
@@ -31529,10 +31524,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>530006.1848296403</v>
+        <v>529850.4308464682</v>
       </c>
       <c r="R277" t="n">
-        <v>7207854.649634163</v>
+        <v>7207963.126348528</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -31601,10 +31596,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>89169170</v>
+        <v>89169157</v>
       </c>
       <c r="B278" t="n">
-        <v>89780</v>
+        <v>78602</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -31617,21 +31612,21 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>4217</v>
+        <v>6463</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
@@ -31641,10 +31636,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>529850.4308464682</v>
+        <v>529626.1508865874</v>
       </c>
       <c r="R278" t="n">
-        <v>7207963.126348528</v>
+        <v>7208188.997705467</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -31713,10 +31708,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>89169157</v>
+        <v>90781432</v>
       </c>
       <c r="B279" t="n">
-        <v>78602</v>
+        <v>90023</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -31725,41 +31720,52 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>6463</v>
+        <v>3014</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Parasitporing</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Antrodiella parasitica</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I279" t="inlineStr"/>
+          <t>Vampola</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Rödingsjöbäcken, Njakafjäll, Ås lm</t>
+          <t>Sventkullen, Njakafjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>529626.1508865874</v>
+        <v>530898.800436235</v>
       </c>
       <c r="R279" t="n">
-        <v>7208188.997705467</v>
+        <v>7208980.064429437</v>
       </c>
       <c r="S279" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T279" t="inlineStr">
         <is>
@@ -31783,7 +31789,7 @@
       </c>
       <c r="Y279" t="inlineStr">
         <is>
-          <t>2020-11-19</t>
+          <t>2020-09-19</t>
         </is>
       </c>
       <c r="Z279" t="inlineStr">
@@ -31793,7 +31799,7 @@
       </c>
       <c r="AA279" t="inlineStr">
         <is>
-          <t>2020-11-19</t>
+          <t>2020-09-19</t>
         </is>
       </c>
       <c r="AB279" t="inlineStr">
@@ -31807,8 +31813,34 @@
       <c r="AE279" t="b">
         <v>0</v>
       </c>
+      <c r="AF279" t="inlineStr"/>
       <c r="AG279" t="b">
         <v>0</v>
+      </c>
+      <c r="AH279" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ279" t="inlineStr">
+        <is>
+          <t>violticka</t>
+        </is>
+      </c>
+      <c r="AK279" t="inlineStr">
+        <is>
+          <t>Trichaptum abietinum</t>
+        </is>
+      </c>
+      <c r="AM279" t="inlineStr">
+        <is>
+          <t>Svamp, fruktkropp mm</t>
+        </is>
+      </c>
+      <c r="AO279" t="inlineStr">
+        <is>
+          <t>Fungi, fruit bodies, etc. # På violticka på granlåga # Trichaptum abietinum</t>
+        </is>
       </c>
       <c r="AT279" t="inlineStr"/>
       <c r="AW279" t="inlineStr">
@@ -31818,159 +31850,10 @@
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Alexina Brännlund, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
-    </row>
-    <row r="280">
-      <c r="A280" t="n">
-        <v>90781432</v>
-      </c>
-      <c r="B280" t="n">
-        <v>90023</v>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E280" t="n">
-        <v>3014</v>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>Parasitporing</t>
-        </is>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>Antrodiella parasitica</t>
-        </is>
-      </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>Vampola</t>
-        </is>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J280" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K280" t="inlineStr"/>
-      <c r="N280" t="inlineStr"/>
-      <c r="P280" t="inlineStr">
-        <is>
-          <t>Sventkullen, Njakafjäll, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q280" t="n">
-        <v>530898.800436235</v>
-      </c>
-      <c r="R280" t="n">
-        <v>7208980.064429437</v>
-      </c>
-      <c r="S280" t="n">
-        <v>25</v>
-      </c>
-      <c r="T280" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U280" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V280" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W280" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y280" t="inlineStr">
-        <is>
-          <t>2020-09-19</t>
-        </is>
-      </c>
-      <c r="Z280" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA280" t="inlineStr">
-        <is>
-          <t>2020-09-19</t>
-        </is>
-      </c>
-      <c r="AB280" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD280" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE280" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF280" t="inlineStr"/>
-      <c r="AG280" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH280" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ280" t="inlineStr">
-        <is>
-          <t>violticka</t>
-        </is>
-      </c>
-      <c r="AK280" t="inlineStr">
-        <is>
-          <t>Trichaptum abietinum</t>
-        </is>
-      </c>
-      <c r="AM280" t="inlineStr">
-        <is>
-          <t>Svamp, fruktkropp mm</t>
-        </is>
-      </c>
-      <c r="AO280" t="inlineStr">
-        <is>
-          <t>Fungi, fruit bodies, etc. # På violticka på granlåga # Trichaptum abietinum</t>
-        </is>
-      </c>
-      <c r="AT280" t="inlineStr"/>
-      <c r="AW280" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX280" t="inlineStr">
-        <is>
-          <t>Isak Vahlström, Alexina Brännlund, Yasmine Kindlund</t>
-        </is>
-      </c>
-      <c r="AY280" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
